--- a/data/trans_dic/P62A$otras-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,47 +727,47 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70,08; 100,0</t>
+          <t>62,99; 100,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,33</t>
+          <t>0,0; 66,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,64; 61,87</t>
+          <t>13,05; 63,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,9; 73,73</t>
+          <t>22,29; 78,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 88,54</t>
+          <t>0,0; 88,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,54; 84,35</t>
+          <t>20,12; 83,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,79; 92,64</t>
+          <t>56,32; 95,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,49; 100,0</t>
+          <t>54,33; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,92; 100,0</t>
+          <t>39,71; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,16; 67,83</t>
+          <t>18,74; 68,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,71; 76,34</t>
+          <t>46,31; 76,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,65; 82,5</t>
+          <t>48,76; 82,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,17; 89,79</t>
+          <t>44,89; 87,95</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,21</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,8; 59,36</t>
+          <t>28,54; 60,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,35; 59,81</t>
+          <t>24,46; 60,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,31; 76,79</t>
+          <t>30,41; 75,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 38,28</t>
+          <t>4,88; 37,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,83; 61,79</t>
+          <t>28,24; 61,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,44; 72,64</t>
+          <t>39,04; 74,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,62; 78,05</t>
+          <t>45,64; 76,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 23,74</t>
+          <t>4,15; 24,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,96; 57,78</t>
+          <t>32,79; 56,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,28; 62,7</t>
+          <t>36,12; 61,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,42; 72,54</t>
+          <t>44,89; 71,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,58</t>
+          <t>0,0; 13,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 29,71</t>
+          <t>10,65; 29,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,44; 34,72</t>
+          <t>14,55; 33,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,35; 47,36</t>
+          <t>20,89; 45,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 27,25</t>
+          <t>7,03; 26,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 44,42</t>
+          <t>18,52; 44,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 32,95</t>
+          <t>9,08; 31,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,05; 53,49</t>
+          <t>30,05; 54,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 15,05</t>
+          <t>3,39; 14,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 33,02</t>
+          <t>17,18; 32,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 29,44</t>
+          <t>14,42; 30,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,8; 45,48</t>
+          <t>27,97; 45,56</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,85</t>
+          <t>4,81; 14,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,29</t>
+          <t>4,37; 12,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,56; 37,8</t>
+          <t>24,09; 37,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,0</t>
+          <t>1,22; 11,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 15,32</t>
+          <t>3,27; 16,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 17,77</t>
+          <t>4,65; 18,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,98; 36,24</t>
+          <t>22,24; 36,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,72</t>
+          <t>0,4; 4,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 12,72</t>
+          <t>5,3; 12,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,82</t>
+          <t>5,51; 11,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 35,3</t>
+          <t>25,1; 34,58</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,82; 33,12</t>
+          <t>24,88; 32,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,81</t>
+          <t>0,5; 4,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,34</t>
+          <t>3,12; 9,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 13,81</t>
+          <t>6,41; 14,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 22,67</t>
+          <t>3,45; 22,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,11</t>
+          <t>0,36; 2,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,2</t>
+          <t>1,5; 4,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,41</t>
+          <t>2,62; 6,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,03; 26,47</t>
+          <t>7,87; 26,43</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,89; 32,47</t>
+          <t>23,94; 32,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,69</t>
+          <t>0,46; 4,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,38</t>
+          <t>1,84; 6,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 14,35</t>
+          <t>6,09; 14,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,7; 12,63</t>
+          <t>7,61; 12,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,41</t>
+          <t>0,25; 2,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,84</t>
+          <t>1,0; 4,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,06</t>
+          <t>3,4; 7,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,38; 20,2</t>
+          <t>15,37; 20,43</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,74</t>
+          <t>0,38; 1,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,9</t>
+          <t>5,23; 8,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,29</t>
+          <t>4,98; 8,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,24; 33,18</t>
+          <t>27,09; 33,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,74</t>
+          <t>3,0; 6,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,5; 15,47</t>
+          <t>10,42; 15,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,48</t>
+          <t>12,25; 17,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 21,49</t>
+          <t>8,34; 21,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,53</t>
+          <t>1,83; 3,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,3</t>
+          <t>8,13; 11,32</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,01</t>
+          <t>8,88; 11,91</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,7; 26,17</t>
+          <t>14,67; 26,29</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>212; 927</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2078,47 +2078,47 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2858; 4483</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>455; 1990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>226; 988</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7864; 9677</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8955; 10621</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1860</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>825; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9537; 13608</t>
+          <t>8572; 13608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13317; 15104</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3414</t>
+          <t>0; 3471</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2117; 10363</t>
+          <t>2185; 10712</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3163; 10646</t>
+          <t>3218; 11366</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1276; 7192</t>
+          <t>0; 7166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2322; 9093</t>
+          <t>2168; 8996</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13333; 22544</t>
+          <t>13705; 23270</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7901; 12850</t>
+          <t>6982; 12850</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4691; 12055</t>
+          <t>4787; 12055</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3067; 10856</t>
+          <t>2999; 10935</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18369; 31365</t>
+          <t>19028; 31588</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13277; 22513</t>
+          <t>13306; 22546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8508; 18119</t>
+          <t>9057; 17746</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6319</t>
+          <t>0; 5974</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13458; 27735</t>
+          <t>13334; 28487</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6895; 17659</t>
+          <t>7223; 17853</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6022; 15259</t>
+          <t>6042; 14987</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>902; 7384</t>
+          <t>941; 7266</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11040; 24509</t>
+          <t>11201; 24340</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10727; 20809</t>
+          <t>11184; 21222</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12312; 20178</t>
+          <t>11799; 19704</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1853; 10530</t>
+          <t>1843; 10885</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28477; 49915</t>
+          <t>28327; 48825</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21103; 36476</t>
+          <t>21012; 35994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20768; 33170</t>
+          <t>20528; 32738</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4388</t>
+          <t>0; 6357</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7735; 22527</t>
+          <t>8075; 22256</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10589; 27366</t>
+          <t>11471; 26463</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11112; 25857</t>
+          <t>11406; 24976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1983; 11188</t>
+          <t>2885; 10859</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10228; 24269</t>
+          <t>10118; 24046</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4140; 15596</t>
+          <t>4300; 14888</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11605; 21366</t>
+          <t>12005; 21578</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2903; 13075</t>
+          <t>2947; 12904</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21344; 43085</t>
+          <t>22418; 42815</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18521; 37143</t>
+          <t>18191; 38261</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25338; 42999</t>
+          <t>26441; 43071</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4661</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8375; 24018</t>
+          <t>8347; 24497</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9061; 24623</t>
+          <t>8745; 25397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41812; 64346</t>
+          <t>40998; 63699</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>980; 8790</t>
+          <t>974; 9127</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3647; 14666</t>
+          <t>3132; 15977</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5337; 19723</t>
+          <t>5163; 19993</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24400; 38489</t>
+          <t>23614; 38298</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>978; 9251</t>
+          <t>991; 10341</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14448; 34230</t>
+          <t>14262; 34539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16813; 36789</t>
+          <t>17155; 37024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69824; 97578</t>
+          <t>69385; 95588</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4978</t>
+          <t>0; 4816</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4995</t>
+          <t>0; 5267</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4451</t>
+          <t>0; 5229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74340; 99186</t>
+          <t>74525; 98235</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>852; 8507</t>
+          <t>888; 7875</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6908; 21063</t>
+          <t>7028; 20732</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14040; 32321</t>
+          <t>15012; 34371</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16731; 97762</t>
+          <t>14875; 96165</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1671; 9740</t>
+          <t>1658; 9665</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7974; 22311</t>
+          <t>7951; 22602</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15861; 35744</t>
+          <t>14613; 34573</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51403; 193446</t>
+          <t>57518; 193163</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1825</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2150</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4613</t>
+          <t>0; 5017</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59038; 80259</t>
+          <t>59180; 80220</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1121; 11607</t>
+          <t>1135; 11570</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6335; 21887</t>
+          <t>5465; 20731</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18256; 41979</t>
+          <t>17830; 42691</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24558; 40288</t>
+          <t>24285; 38875</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1121; 10938</t>
+          <t>1126; 11742</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5445; 20953</t>
+          <t>5431; 22292</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18416; 43743</t>
+          <t>18438; 43106</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>87075; 114388</t>
+          <t>87002; 115680</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2732; 12874</t>
+          <t>2795; 13718</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>45598; 77561</t>
+          <t>45583; 76997</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44216; 74670</t>
+          <t>44849; 75868</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>218331; 265915</t>
+          <t>217117; 264657</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18477; 38851</t>
+          <t>17283; 39179</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78344; 115435</t>
+          <t>77718; 118426</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>89612; 128867</t>
+          <t>90297; 132020</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>77601; 201462</t>
+          <t>78212; 203284</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>23706; 46446</t>
+          <t>23990; 48784</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>132079; 182666</t>
+          <t>131474; 183044</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>142716; 196679</t>
+          <t>145433; 195121</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>255724; 455137</t>
+          <t>255174; 457237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$otras-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Edad-trans_dic.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,99; 100,0</t>
+          <t>68,22; 100,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,42</t>
+          <t>0,0; 78,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,05; 63,95</t>
+          <t>12,64; 61,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,29; 78,71</t>
+          <t>28,34; 79,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 88,22</t>
+          <t>16,13; 88,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,12; 83,45</t>
+          <t>21,31; 83,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,32; 95,62</t>
+          <t>56,41; 95,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,33; 100,0</t>
+          <t>58,04; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,71; 100,0</t>
+          <t>48,52; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,74; 68,32</t>
+          <t>18,58; 67,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,31; 76,89</t>
+          <t>46,41; 76,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,76; 82,62</t>
+          <t>48,43; 85,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,89; 87,95</t>
+          <t>46,08; 89,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,54; 60,97</t>
+          <t>28,1; 59,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,46; 60,47</t>
+          <t>22,06; 60,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,41; 75,42</t>
+          <t>29,18; 74,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 37,67</t>
+          <t>4,8; 36,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,24; 61,36</t>
+          <t>28,51; 61,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,04; 74,08</t>
+          <t>35,62; 74,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45,64; 76,22</t>
+          <t>47,13; 77,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 24,54</t>
+          <t>4,19; 23,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,79; 56,52</t>
+          <t>32,83; 56,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,12; 61,88</t>
+          <t>35,32; 61,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,89; 71,6</t>
+          <t>44,57; 70,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,88</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 29,35</t>
+          <t>10,16; 29,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 33,57</t>
+          <t>14,81; 35,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,89; 45,75</t>
+          <t>23,15; 48,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 26,45</t>
+          <t>4,87; 26,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,52; 44,01</t>
+          <t>19,22; 45,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 31,45</t>
+          <t>8,79; 32,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,05; 54,02</t>
+          <t>32,66; 56,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 14,86</t>
+          <t>3,4; 14,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 32,82</t>
+          <t>16,56; 32,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 30,33</t>
+          <t>14,43; 29,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 45,56</t>
+          <t>30,97; 48,27</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 14,13</t>
+          <t>4,71; 14,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,68</t>
+          <t>4,34; 11,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,09; 37,42</t>
+          <t>25,25; 38,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,42</t>
+          <t>1,22; 10,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 16,69</t>
+          <t>3,37; 15,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 18,01</t>
+          <t>4,65; 16,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,24; 36,06</t>
+          <t>23,65; 36,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,16</t>
+          <t>0,48; 3,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 12,83</t>
+          <t>5,43; 12,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,89</t>
+          <t>5,48; 12,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,1; 34,58</t>
+          <t>25,78; 35,39</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,88; 32,8</t>
+          <t>25,41; 33,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,46</t>
+          <t>0,5; 4,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,19</t>
+          <t>3,06; 8,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 14,69</t>
+          <t>6,37; 14,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 22,3</t>
+          <t>17,83; 24,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,09</t>
+          <t>0,36; 2,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,25</t>
+          <t>1,52; 4,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,2</t>
+          <t>2,71; 6,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 26,43</t>
+          <t>23,02; 28,88</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1567,52 +1567,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,94; 32,46</t>
+          <t>23,94; 33,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,68</t>
+          <t>0,53; 4,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,99</t>
+          <t>2,09; 6,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 14,59</t>
+          <t>6,1; 14,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,19</t>
+          <t>7,54; 12,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,59</t>
+          <t>0,25; 2,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,09</t>
+          <t>1,01; 4,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,94</t>
+          <t>3,54; 7,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,37; 20,43</t>
+          <t>15,24; 20,54</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,86</t>
+          <t>0,37; 1,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,84</t>
+          <t>5,1; 8,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,42</t>
+          <t>5,02; 8,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,09; 33,02</t>
+          <t>27,97; 33,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,8</t>
+          <t>3,25; 6,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,87</t>
+          <t>10,59; 15,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,25; 17,91</t>
+          <t>12,05; 17,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,34; 21,68</t>
+          <t>18,69; 23,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,71</t>
+          <t>1,8; 3,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,32</t>
+          <t>8,15; 11,23</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,88; 11,91</t>
+          <t>8,79; 11,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,67; 26,29</t>
+          <t>24,34; 28,08</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8572; 13608</t>
+          <t>9283; 13608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5258</t>
+          <t>0; 4914</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>15178</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3471</t>
+          <t>0; 4084</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2185; 10712</t>
+          <t>2117; 10377</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3218; 11366</t>
+          <t>4093; 11518</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7166</t>
+          <t>1349; 7358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2168; 8996</t>
+          <t>2297; 8964</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13705; 23270</t>
+          <t>13728; 23247</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6982; 12850</t>
+          <t>7458; 12850</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4787; 12055</t>
+          <t>6379; 13146</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2999; 10935</t>
+          <t>2974; 10836</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19028; 31588</t>
+          <t>19067; 31227</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13306; 22546</t>
+          <t>13215; 23239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9057; 17746</t>
+          <t>9911; 19265</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>28230</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5974</t>
+          <t>0; 5954</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13334; 28487</t>
+          <t>13130; 27736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7223; 17853</t>
+          <t>6513; 17754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6042; 14987</t>
+          <t>6079; 15505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>941; 7266</t>
+          <t>926; 7009</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11201; 24340</t>
+          <t>11309; 24503</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11184; 21222</t>
+          <t>10204; 21245</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11799; 19704</t>
+          <t>13165; 21533</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1843; 10885</t>
+          <t>1858; 10222</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28327; 48825</t>
+          <t>28360; 48610</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21012; 35994</t>
+          <t>20547; 36021</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20528; 32738</t>
+          <t>21736; 34394</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>41394</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6357</t>
+          <t>0; 4368</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8075; 22256</t>
+          <t>7703; 22705</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11471; 26463</t>
+          <t>11670; 27991</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11406; 24976</t>
+          <t>14054; 29507</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2885; 10859</t>
+          <t>1998; 10992</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10118; 24046</t>
+          <t>10499; 24601</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4300; 14888</t>
+          <t>4163; 15453</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12005; 21578</t>
+          <t>14607; 25121</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2947; 12904</t>
+          <t>2957; 12985</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22418; 42815</t>
+          <t>21607; 42789</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18191; 38261</t>
+          <t>18206; 37584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26441; 43071</t>
+          <t>32659; 50892</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51405</t>
+          <t>56250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82202</t>
+          <t>90964</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4244</t>
+          <t>0; 3979</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8347; 24497</t>
+          <t>8172; 25320</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8745; 25397</t>
+          <t>8685; 23951</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40998; 63699</t>
+          <t>45336; 68720</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>974; 9127</t>
+          <t>978; 8420</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3132; 15977</t>
+          <t>3225; 14728</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5163; 19993</t>
+          <t>5166; 18558</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23614; 38298</t>
+          <t>27769; 43095</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>991; 10341</t>
+          <t>1206; 9784</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14262; 34539</t>
+          <t>14628; 33994</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17155; 37024</t>
+          <t>17054; 37614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69385; 95588</t>
+          <t>76531; 105067</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86686</t>
+          <t>97995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>47741</t>
+          <t>52548</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>134426</t>
+          <t>150543</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4816</t>
+          <t>0; 5045</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5267</t>
+          <t>0; 5697</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5229</t>
+          <t>0; 6157</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74525; 98235</t>
+          <t>84254; 111133</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>888; 7875</t>
+          <t>882; 7814</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7028; 20732</t>
+          <t>6898; 20119</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15012; 34371</t>
+          <t>14919; 32963</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14875; 96165</t>
+          <t>44387; 62018</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1658; 9665</t>
+          <t>1683; 9590</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7951; 22602</t>
+          <t>8083; 22701</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14613; 34573</t>
+          <t>15099; 35234</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57518; 193163</t>
+          <t>133641; 167626</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69347</t>
+          <t>76661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>100902</t>
+          <t>110533</t>
         </is>
       </c>
     </row>
@@ -3326,52 +3326,52 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5017</t>
+          <t>0; 3645</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59180; 80220</t>
+          <t>65030; 89731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1135; 11570</t>
+          <t>1318; 11407</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5465; 20731</t>
+          <t>6184; 20482</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17830; 42691</t>
+          <t>17847; 42307</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24285; 38875</t>
+          <t>26278; 43730</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1126; 11742</t>
+          <t>1126; 12642</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5431; 22292</t>
+          <t>5486; 21799</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18438; 43106</t>
+          <t>19219; 43401</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>87002; 115680</t>
+          <t>94512; 127405</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>269735</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>152188</t>
+          <t>168859</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>394527</t>
+          <t>438594</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2795; 13718</t>
+          <t>2753; 12746</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>45583; 76997</t>
+          <t>44464; 77035</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44849; 75868</t>
+          <t>45244; 76195</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>217117; 264657</t>
+          <t>244560; 294498</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17283; 39179</t>
+          <t>18706; 40171</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>77718; 118426</t>
+          <t>78999; 119181</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90297; 132020</t>
+          <t>88792; 129165</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>78212; 203284</t>
+          <t>150263; 186524</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>23990; 48784</t>
+          <t>23649; 46759</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>131474; 183044</t>
+          <t>131836; 181554</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>145433; 195121</t>
+          <t>144074; 193592</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>255174; 457237</t>
+          <t>408488; 471254</t>
         </is>
       </c>
     </row>
